--- a/Accounting 1.xlsx
+++ b/Accounting 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baby\Desktop\2nd Sem. MOD.2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baby\Desktop\New folder\2nd Sem. MOD.2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2DC94B9-A0E0-416B-8ECA-6CDD46C87660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44D7A093-3F9C-473D-9613-2C7CB479DC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3D059A5D-A0A8-49E2-B973-69C7AA10263E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B3C88588-BD18-430A-96D0-20E0C0910A51}"/>
   </bookViews>
   <sheets>
     <sheet name="2nd Sem.MOD.2025(Accounting 1)" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="140">
   <si>
     <t xml:space="preserve">                       METRO BUSINESS COLLEGE</t>
   </si>
@@ -306,9 +306,6 @@
   </si>
   <si>
     <t xml:space="preserve">                                  OD=OFFICIALLY DROPPED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                       Subject: Subject: Accounting 1</t>
   </si>
   <si>
     <t>Cuya, Emely Rae D.</t>
@@ -826,7 +823,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="Image result for metro business college logo">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3F75BDB-EA77-42BF-BA5D-5E6C60CBFF5F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26E76559-D493-4712-B2DA-5FFF8E21115C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -900,7 +897,7 @@
         <xdr:cNvPr id="3" name="Picture 1" descr="Image result for metro business college logo">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08A1F750-18CC-4844-A388-7019FF38E712}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86C1D77A-397E-4FF9-96F0-063B29516167}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -974,7 +971,7 @@
         <xdr:cNvPr id="4" name="Picture 3" descr="Image result for metro business college logo">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{035F66C9-8BD5-4284-A6F2-CFD9B157F22F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47C3A5B8-58CF-46A2-9F07-8FE8CEB61AA9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1048,7 +1045,7 @@
         <xdr:cNvPr id="5" name="Picture 1" descr="Image result for metro business college logo">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{598ABD24-A84B-48A6-830B-D8D0A9EEFAC9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62D3A36F-3ADE-4EFC-949B-C24EA5B12323}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1122,7 +1119,7 @@
         <xdr:cNvPr id="6" name="Picture 5" descr="Image result for metro business college logo">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1707378-7D2C-4D8D-840B-2A5AB1135BB9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2072C1CC-950C-4FB9-BC00-8F86ED3B6F56}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1196,7 +1193,7 @@
         <xdr:cNvPr id="7" name="Picture 1" descr="Image result for metro business college logo">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{106BB245-601D-4261-8660-9C66E83B9036}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5239F102-B97D-4BAE-9094-DF27A28C1931}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1270,7 +1267,7 @@
         <xdr:cNvPr id="8" name="Picture 7" descr="Image result for metro business college logo">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{323CEB3B-2096-4171-A4C6-D39D30B4C63D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C139B49-1285-4F06-B7F1-4C6E20E50C9E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1344,7 +1341,7 @@
         <xdr:cNvPr id="9" name="Picture 1" descr="Image result for metro business college logo">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{518A7FA8-659E-4D77-8802-3D3F730E5C5C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68EBA8B4-FD62-4E62-AD61-C13A51001963}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1699,7 +1696,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F85439E0-C277-4806-9C1A-0D9060CC58A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{289B873B-D724-4BE8-BE00-EA1FC7D3709B}">
   <dimension ref="A2:J180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2226,7 +2223,7 @@
     </row>
     <row r="52" spans="1:10" ht="15.75">
       <c r="B52" s="6" t="s">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="D52" s="6"/>
       <c r="G52" s="7" t="s">
@@ -2296,14 +2293,14 @@
         <v>16</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C58" s="16"/>
       <c r="D58" s="16"/>
       <c r="E58" s="16"/>
       <c r="F58" s="16"/>
       <c r="G58" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H58" s="16"/>
       <c r="I58" s="16"/>
@@ -2314,14 +2311,14 @@
         <v>17</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C59" s="16"/>
       <c r="D59" s="16"/>
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
       <c r="G59" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H59" s="16"/>
       <c r="I59" s="16"/>
@@ -2332,14 +2329,14 @@
         <v>18</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C60" s="16"/>
       <c r="D60" s="16"/>
       <c r="E60" s="16"/>
       <c r="F60" s="16"/>
       <c r="G60" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H60" s="16"/>
       <c r="I60" s="16"/>
@@ -2350,14 +2347,14 @@
         <v>19</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C61" s="16"/>
       <c r="D61" s="16"/>
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
       <c r="G61" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H61" s="16"/>
       <c r="I61" s="16"/>
@@ -2368,14 +2365,14 @@
         <v>20</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C62" s="16"/>
       <c r="D62" s="16"/>
       <c r="E62" s="16"/>
       <c r="F62" s="16"/>
       <c r="G62" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H62" s="16"/>
       <c r="I62" s="16"/>
@@ -2386,14 +2383,14 @@
         <v>21</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C63" s="16"/>
       <c r="D63" s="16"/>
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
       <c r="G63" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H63" s="16"/>
       <c r="I63" s="16"/>
@@ -2404,14 +2401,14 @@
         <v>22</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C64" s="16"/>
       <c r="D64" s="16"/>
       <c r="E64" s="16"/>
       <c r="F64" s="16"/>
       <c r="G64" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H64" s="16"/>
       <c r="I64" s="16"/>
@@ -2422,14 +2419,14 @@
         <v>23</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C65" s="16"/>
       <c r="D65" s="16"/>
       <c r="E65" s="16"/>
       <c r="F65" s="16"/>
       <c r="G65" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H65" s="16"/>
       <c r="I65" s="16"/>
@@ -2440,14 +2437,14 @@
         <v>24</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C66" s="16"/>
       <c r="D66" s="16"/>
       <c r="E66" s="16"/>
       <c r="F66" s="16"/>
       <c r="G66" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H66" s="16"/>
       <c r="I66" s="16"/>
@@ -2458,14 +2455,14 @@
         <v>25</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C67" s="16"/>
       <c r="D67" s="16"/>
       <c r="E67" s="16"/>
       <c r="F67" s="16"/>
       <c r="G67" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H67" s="16"/>
       <c r="I67" s="16"/>
@@ -2476,14 +2473,14 @@
         <v>26</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C68" s="16"/>
       <c r="D68" s="16"/>
       <c r="E68" s="16"/>
       <c r="F68" s="16"/>
       <c r="G68" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H68" s="16"/>
       <c r="I68" s="16"/>
@@ -2494,14 +2491,14 @@
         <v>27</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C69" s="16"/>
       <c r="D69" s="16"/>
       <c r="E69" s="16"/>
       <c r="F69" s="16"/>
       <c r="G69" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H69" s="16"/>
       <c r="I69" s="16"/>
@@ -2512,14 +2509,14 @@
         <v>28</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C70" s="16"/>
       <c r="D70" s="16"/>
       <c r="E70" s="16"/>
       <c r="F70" s="16"/>
       <c r="G70" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H70" s="16"/>
       <c r="I70" s="16"/>
@@ -2530,14 +2527,14 @@
         <v>29</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C71" s="16"/>
       <c r="D71" s="16"/>
       <c r="E71" s="16"/>
       <c r="F71" s="16"/>
       <c r="G71" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H71" s="16"/>
       <c r="I71" s="16"/>
@@ -2548,14 +2545,14 @@
         <v>30</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C72" s="16"/>
       <c r="D72" s="16"/>
       <c r="E72" s="16"/>
       <c r="F72" s="16"/>
       <c r="G72" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H72" s="16"/>
       <c r="I72" s="16"/>
@@ -2783,14 +2780,14 @@
         <v>31</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C103" s="16"/>
       <c r="D103" s="16"/>
       <c r="E103" s="16"/>
       <c r="F103" s="16"/>
       <c r="G103" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H103" s="16"/>
       <c r="I103" s="16"/>
@@ -2801,14 +2798,14 @@
         <v>32</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C104" s="16"/>
       <c r="D104" s="16"/>
       <c r="E104" s="16"/>
       <c r="F104" s="16"/>
       <c r="G104" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H104" s="16"/>
       <c r="I104" s="16"/>
@@ -2819,14 +2816,14 @@
         <v>33</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C105" s="16"/>
       <c r="D105" s="16"/>
       <c r="E105" s="16"/>
       <c r="F105" s="16"/>
       <c r="G105" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H105" s="16"/>
       <c r="I105" s="16"/>
@@ -2837,14 +2834,14 @@
         <v>34</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C106" s="16"/>
       <c r="D106" s="16"/>
       <c r="E106" s="16"/>
       <c r="F106" s="16"/>
       <c r="G106" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H106" s="16"/>
       <c r="I106" s="16"/>
@@ -2855,14 +2852,14 @@
         <v>35</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C107" s="16"/>
       <c r="D107" s="16"/>
       <c r="E107" s="16"/>
       <c r="F107" s="16"/>
       <c r="G107" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H107" s="16"/>
       <c r="I107" s="16"/>
@@ -2873,14 +2870,14 @@
         <v>36</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C108" s="16"/>
       <c r="D108" s="16"/>
       <c r="E108" s="16"/>
       <c r="F108" s="16"/>
       <c r="G108" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H108" s="16"/>
       <c r="I108" s="16"/>
@@ -2891,14 +2888,14 @@
         <v>37</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C109" s="16"/>
       <c r="D109" s="16"/>
       <c r="E109" s="16"/>
       <c r="F109" s="16"/>
       <c r="G109" s="17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H109" s="16"/>
       <c r="I109" s="16"/>
@@ -2909,14 +2906,14 @@
         <v>38</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C110" s="16"/>
       <c r="D110" s="16"/>
       <c r="E110" s="16"/>
       <c r="F110" s="16"/>
       <c r="G110" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H110" s="16"/>
       <c r="I110" s="16"/>
@@ -2927,14 +2924,14 @@
         <v>39</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C111" s="16"/>
       <c r="D111" s="16"/>
       <c r="E111" s="16"/>
       <c r="F111" s="16"/>
       <c r="G111" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H111" s="16"/>
       <c r="I111" s="16"/>
@@ -2945,14 +2942,14 @@
         <v>40</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C112" s="16"/>
       <c r="D112" s="16"/>
       <c r="E112" s="16"/>
       <c r="F112" s="16"/>
       <c r="G112" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H112" s="16"/>
       <c r="I112" s="16"/>
@@ -2963,14 +2960,14 @@
         <v>41</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C113" s="16"/>
       <c r="D113" s="16"/>
       <c r="E113" s="16"/>
       <c r="F113" s="16"/>
       <c r="G113" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H113" s="16"/>
       <c r="I113" s="16"/>
@@ -2981,14 +2978,14 @@
         <v>42</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C114" s="16"/>
       <c r="D114" s="16"/>
       <c r="E114" s="16"/>
       <c r="F114" s="16"/>
       <c r="G114" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H114" s="16"/>
       <c r="I114" s="16"/>
@@ -2999,14 +2996,14 @@
         <v>43</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C115" s="16"/>
       <c r="D115" s="16"/>
       <c r="E115" s="16"/>
       <c r="F115" s="16"/>
       <c r="G115" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H115" s="16"/>
       <c r="I115" s="16"/>
@@ -3017,14 +3014,14 @@
         <v>44</v>
       </c>
       <c r="B116" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C116" s="31"/>
       <c r="D116" s="31"/>
       <c r="E116" s="31"/>
       <c r="F116" s="31"/>
       <c r="G116" s="32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H116" s="31"/>
       <c r="I116" s="31"/>
@@ -3035,7 +3032,7 @@
         <v>45</v>
       </c>
       <c r="B117" s="34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C117" s="16"/>
       <c r="D117" s="16"/>
@@ -3271,14 +3268,14 @@
         <v>46</v>
       </c>
       <c r="B148" s="34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C148" s="16"/>
       <c r="D148" s="16"/>
       <c r="E148" s="16"/>
       <c r="F148" s="16"/>
       <c r="G148" s="17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H148" s="16"/>
       <c r="I148" s="16"/>
@@ -3289,14 +3286,14 @@
         <v>47</v>
       </c>
       <c r="B149" s="34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C149" s="16"/>
       <c r="D149" s="16"/>
       <c r="E149" s="16"/>
       <c r="F149" s="16"/>
       <c r="G149" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H149" s="16"/>
       <c r="I149" s="16"/>
@@ -3307,14 +3304,14 @@
         <v>48</v>
       </c>
       <c r="B150" s="34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C150" s="16"/>
       <c r="D150" s="16"/>
       <c r="E150" s="16"/>
       <c r="F150" s="16"/>
       <c r="G150" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H150" s="16"/>
       <c r="I150" s="16"/>
@@ -3325,14 +3322,14 @@
         <v>49</v>
       </c>
       <c r="B151" s="34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C151" s="16"/>
       <c r="D151" s="16"/>
       <c r="E151" s="16"/>
       <c r="F151" s="16"/>
       <c r="G151" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H151" s="16"/>
       <c r="I151" s="16"/>
@@ -3343,14 +3340,14 @@
         <v>50</v>
       </c>
       <c r="B152" s="34" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C152" s="16"/>
       <c r="D152" s="16"/>
       <c r="E152" s="16"/>
       <c r="F152" s="16"/>
       <c r="G152" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H152" s="16"/>
       <c r="I152" s="16"/>
